--- a/betraja/locales-excel/betraja_translations.xlsx
+++ b/betraja/locales-excel/betraja_translations.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G568"/>
+  <dimension ref="A1:G580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15932,32 +15932,32 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>brandDefault</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>About</t>
+          <t>Brand default</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>અમારા વિશે</t>
+          <t>બ્રાન્ડ ડિફૉલ્ટ</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>हमारे बारे में</t>
+          <t>ब्रांड डिफ़ॉल्ट</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>எங்களைப் பற்றி</t>
+          <t>பிராண்ட் இயல்புநிலை</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>మా గురించి</t>
+          <t>బ్రాండ్ డిఫాల్ట్</t>
         </is>
       </c>
     </row>
@@ -15969,32 +15969,32 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>banner</t>
+          <t>button</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>Layout</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>બેનર</t>
+          <t>લેઆઉટ</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>बैनर</t>
+          <t>लेआउट</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>பேனர்</t>
+          <t>லேஅவுட்</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>బ్యానర్</t>
+          <t>లేఅవుట్</t>
         </is>
       </c>
     </row>
@@ -16006,32 +16006,32 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>button</t>
+          <t>close</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Layout</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>લેઆઉટ</t>
+          <t>બંધ કરો</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>लेआउट</t>
+          <t>बंद करें</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>லேஅவுட்</t>
+          <t>மூடு</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>లేఅవుట్</t>
+          <t>మూసివేయి</t>
         </is>
       </c>
     </row>
@@ -16043,32 +16043,32 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>close</t>
+          <t>colors</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Close</t>
+          <t>Colours</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>બંધ કરો</t>
+          <t>રંગો</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>बंद करें</t>
+          <t>रंग</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>மூடு</t>
+          <t>நிறங்கள்</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>మూసివేయి</t>
+          <t>రంగులు</t>
         </is>
       </c>
     </row>
@@ -16080,32 +16080,32 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>games</t>
+          <t>layouts.classic</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Home games</t>
+          <t>Classic</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>હોમ ગેમ્સ</t>
+          <t>ક્લાસિક</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>होम गेम्स</t>
+          <t>क्लासिक</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>முகப்பு கேம்கள்</t>
+          <t>கிளாசிக்</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>హోమ్ గేమ్స్</t>
+          <t>క్లాసిక్</t>
         </is>
       </c>
     </row>
@@ -16117,32 +16117,32 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>header</t>
+          <t>layouts.grouped</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Grouped</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>હેડર</t>
+          <t>ગ્રુપ્ડ</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>हेडर</t>
+          <t>ग्रुप्ड</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>ஹெடர்</t>
+          <t>குரூப்டு</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>హెడర్</t>
+          <t>గ్రూప్డ్</t>
         </is>
       </c>
     </row>
@@ -16154,32 +16154,32 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>options.bento</t>
+          <t>layouts.modern</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Bento</t>
+          <t>Modern</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>બેન્ટો</t>
+          <t>મોડર્ન</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>बेंटो</t>
+          <t>मॉडर्न</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>பென்டோ</t>
+          <t>மாடர்ன்</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>బెంటో</t>
+          <t>మోడర్న్</t>
         </is>
       </c>
     </row>
@@ -16191,32 +16191,32 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>options.cards</t>
+          <t>layouts.sidebar</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>કાર્ડ્સ</t>
+          <t>સાઇડબાર</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>कार्ड्स</t>
+          <t>साइडबार</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>கார்டுகள்</t>
+          <t>சைட்பார்</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>కార్డ్స్</t>
+          <t>సైడ్‌బార్</t>
         </is>
       </c>
     </row>
@@ -16228,32 +16228,32 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>options.columns</t>
+          <t>palettes.amber</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Columns</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>કૉલમ</t>
+          <t>એમ્બર</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>कॉलम</t>
+          <t>एम्बर</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>நெடுவரிசைகள்</t>
+          <t>ஆம்பர்</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>కాలమ్స్</t>
+          <t>ఆంబర్</t>
         </is>
       </c>
     </row>
@@ -16265,32 +16265,32 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>options.coverflow</t>
+          <t>palettes.aqua</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Coverflow 3D</t>
+          <t>Aqua</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>કવરફ્લો 3D</t>
+          <t>એક્વા</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>कवरफ्लो 3D</t>
+          <t>एक्वा</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>கவர்ஃப்ளோ 3D</t>
+          <t>அக்வா</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>కవర్‌ఫ్లో 3D</t>
+          <t>ఆక్వా</t>
         </is>
       </c>
     </row>
@@ -16302,32 +16302,32 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>options.flat</t>
+          <t>palettes.coral</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Flat</t>
+          <t>Coral</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>ફ્લેટ</t>
+          <t>કોરલ</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>फ्लैट</t>
+          <t>कोरल</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>ஃப்ளாட்</t>
+          <t>கோரல்</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>ఫ్లాట్</t>
+          <t>కోరల్</t>
         </is>
       </c>
     </row>
@@ -16339,32 +16339,32 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>options.grid</t>
+          <t>palettes.crimson</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Crimson</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>ગ્રિડ</t>
+          <t>ક્રિમસન</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>ग्रिड</t>
+          <t>क्रिमसन</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>கிரிட்</t>
+          <t>கிரிம்சன்</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>గ్రిడ్</t>
+          <t>క్రిమ్సన్</t>
         </is>
       </c>
     </row>
@@ -16376,32 +16376,32 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>options.groupnav</t>
+          <t>palettes.emerald</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Group nav</t>
+          <t>Emerald</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>ગ્રુપ નેવ</t>
+          <t>એમરાલ્ડ</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>ग्रुप नेव</t>
+          <t>एमराल्ड</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>குரூப் நேவ்</t>
+          <t>எமரால்டு</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>గ్రూప్ నావ్</t>
+          <t>ఎమరాల్డ్</t>
         </is>
       </c>
     </row>
@@ -16413,32 +16413,32 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>options.hero</t>
+          <t>palettes.flame</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Flame</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>હીરો</t>
+          <t>ફ્લેમ</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>हीरो</t>
+          <t>फ्लेम</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>ஹீரோ</t>
+          <t>ஃப்ளேம்</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>హీరో</t>
+          <t>ఫ్లేమ్</t>
         </is>
       </c>
     </row>
@@ -16450,32 +16450,32 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>options.panels</t>
+          <t>palettes.gold</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Panels</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>પેનલ્સ</t>
+          <t>ગોલ્ડ</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>पैनल्स</t>
+          <t>गोल्ड</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>பேனல்கள்</t>
+          <t>கோல்டு</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>ప్యానెల్స్</t>
+          <t>గోల్డ్</t>
         </is>
       </c>
     </row>
@@ -16487,32 +16487,32 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>options.pillnav</t>
+          <t>palettes.lavender</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Pill nav</t>
+          <t>Lavender</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>પિલ નેવ</t>
+          <t>લેવેન્ડર</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>पिल नेव</t>
+          <t>लैवेंडर</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>பில் நேவ்</t>
+          <t>லாவெண்டர்</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>పిల్ నావ్</t>
+          <t>లావెండర్</t>
         </is>
       </c>
     </row>
@@ -16524,32 +16524,32 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>options.pills</t>
+          <t>palettes.lemon</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Pills</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>પિલ્સ</t>
+          <t>લેમન</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>पिल्स</t>
+          <t>लेमन</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>பில்ஸ்</t>
+          <t>லெமன்</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>పిల్స్</t>
+          <t>లెమన్</t>
         </is>
       </c>
     </row>
@@ -16561,32 +16561,32 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>options.rail</t>
+          <t>palettes.lilac</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Rail</t>
+          <t>Lilac</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>રેલ</t>
+          <t>લાઇલેક</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>रेल</t>
+          <t>लाइलैक</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>ரெயில்</t>
+          <t>லைலாக்</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>రైల్</t>
+          <t>లైలాక్</t>
         </is>
       </c>
     </row>
@@ -16598,32 +16598,32 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>options.showcase</t>
+          <t>palettes.lime</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Showcase</t>
+          <t>Lime</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>શોકેસ</t>
+          <t>લાઇમ</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>शोकेस</t>
+          <t>लाइम</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>ஷோகேஸ்</t>
+          <t>லைம்</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>షోకేస్</t>
+          <t>లైమ్</t>
         </is>
       </c>
     </row>
@@ -16635,32 +16635,32 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>options.sidenav</t>
+          <t>palettes.mint</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Side nav</t>
+          <t>Mint</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>સાઇડ નેવ</t>
+          <t>મિન્ટ</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>साइड नेव</t>
+          <t>मिंट</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>பக்க நேவ்</t>
+          <t>மின்ட்</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>సైడ్ నావ్</t>
+          <t>మింట్</t>
         </is>
       </c>
     </row>
@@ -16672,32 +16672,32 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>options.slider</t>
+          <t>palettes.navy</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Navy</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>સ્લાઇડર</t>
+          <t>નેવી</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>स्लाइडर</t>
+          <t>नेवी</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>ஸ்லைடர்</t>
+          <t>நேவி</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>స్లైడర్</t>
+          <t>నేవీ</t>
         </is>
       </c>
     </row>
@@ -16709,32 +16709,32 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>options.slidercard</t>
+          <t>palettes.ocean</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Slider cards</t>
+          <t>Ocean</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>સ્લાઇડર કાર્ડ</t>
+          <t>ઓશન</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>स्लाइडर कार्ड</t>
+          <t>ओशन</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>ஸ்லைடர் கார்டுகள்</t>
+          <t>ஓஷன்</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>స్లైడర్ కార్డ్స్</t>
+          <t>ఓషన్</t>
         </is>
       </c>
     </row>
@@ -16746,32 +16746,32 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>options.topnav</t>
+          <t>randomize</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Top nav</t>
+          <t>Randomize</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>ટોપ નેવ</t>
+          <t>રેન્ડમ પસંદ કરો</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>टॉप नेव</t>
+          <t>रैंडम चुनें</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>மேல் நேவ்</t>
+          <t>ரேண்டம் தேர்வு</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>టాప్ నావ్</t>
+          <t>రాండమ్ ఎంపిక</t>
         </is>
       </c>
     </row>
@@ -16783,69 +16783,69 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>quicklinks</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Quick links</t>
+          <t>Select a Layout</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>ક્વિક લિંક્સ</t>
+          <t>લેઆઉટ પસંદ કરો</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>क्विक लिंक्स</t>
+          <t>लेआउट चुनें</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>விரைவு இணைப்புகள்</t>
+          <t>லேஅவுட்டைத் தேர்ந்தெடுக்கவும்</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>త్వరిత లింకులు</t>
+          <t>లేఅవుట్‌ను ఎంచుకోండి</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>layoutSwitcher</t>
+          <t>leaderboard</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>end</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Select a Layout</t>
+          <t>End</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>લેઆઉટ પસંદ કરો</t>
+          <t>અંત</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>लेआउट चुनें</t>
+          <t>अंत</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>லேஅவுட்டைத் தேர்ந்தெடுக்கவும்</t>
+          <t>முடிவு</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>లేఅవుట్‌ను ఎంచుకోండి</t>
+          <t>ముగింపు</t>
         </is>
       </c>
     </row>
@@ -16857,32 +16857,32 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>end</t>
+          <t>myRank</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>End</t>
+          <t>My Rank</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>અંત</t>
+          <t>મારો ક્રમ</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>अंत</t>
+          <t>मेरी रैंक</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>முடிவு</t>
+          <t>என் தரவரிசை</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>ముగింపు</t>
+          <t>నా ర్యాంక్</t>
         </is>
       </c>
     </row>
@@ -16894,32 +16894,32 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>myRank</t>
+          <t>noActiveTournaments</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>My Rank</t>
+          <t>Currently no active tournaments</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>મારો ક્રમ</t>
+          <t>હાલ કોઈ સક્રિય ટૂર્નામૅન્ટ નથી</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>मेरी रैंक</t>
+          <t>वर्तमान में कोई सक्रिय टूर्नामेंट नहीं</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>என் தரவரிசை</t>
+          <t>தற்போது செயலில் உள்ள போட்டிகள் இல்லை</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>నా ర్యాంక్</t>
+          <t>ప్రస్తుతం చురుకైన టోర్నమెంట్‌లు లేవు</t>
         </is>
       </c>
     </row>
@@ -16931,32 +16931,32 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>noActiveTournaments</t>
+          <t>noPlayersFound</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Currently no active tournaments</t>
+          <t>No players found</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>હાલ કોઈ સક્રિય ટૂર્નામૅન્ટ નથી</t>
+          <t>કોઈ ખેલાડી મળ્યા નહીં</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>वर्तमान में कोई सक्रिय टूर्नामेंट नहीं</t>
+          <t>कोई खिलाड़ी नहीं मिला</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>தற்போது செயலில் உள்ள போட்டிகள் இல்லை</t>
+          <t>வீரர்கள் எவரும் இல்லை</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>ప్రస్తుతం చురుకైన టోర్నమెంట్‌లు లేవు</t>
+          <t>ప్లేయర్లు ఎవరూ కనుగొనబడలేదు</t>
         </is>
       </c>
     </row>
@@ -16968,32 +16968,32 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>noPlayersFound</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>No players found</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>કોઈ ખેલાડી મળ્યા નહીં</t>
+          <t>ખેલાડી</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>कोई खिलाड़ी नहीं मिला</t>
+          <t>खिलाड़ी</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>வீரர்கள் எவரும் இல்லை</t>
+          <t>வீரர்</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>ప్లేయర్లు ఎవరూ కనుగొనబడలేదు</t>
+          <t>ప్లేయర్</t>
         </is>
       </c>
     </row>
@@ -17005,32 +17005,32 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>points</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Points</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>ખેલાડી</t>
+          <t>પૉઇન્ટ</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>खिलाड़ी</t>
+          <t>अंक</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>வீரர்</t>
+          <t>புள்ளிகள்</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>ప్లేయర్</t>
+          <t>పాయింట్లు</t>
         </is>
       </c>
     </row>
@@ -17042,32 +17042,32 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>points</t>
+          <t>prize</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Points</t>
+          <t>Prize</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>પૉઇન્ટ</t>
+          <t>ઇનામ</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>अंक</t>
+          <t>पुरस्कार</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>புள்ளிகள்</t>
+          <t>பரிசு</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>పాయింట్లు</t>
+          <t>బహుమతి</t>
         </is>
       </c>
     </row>
@@ -17079,32 +17079,32 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>prize</t>
+          <t>rank</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Prize</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>ઇનામ</t>
+          <t>ક્રમ</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>पुरस्कार</t>
+          <t>रैंक</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>பரிசு</t>
+          <t>தரவரிசை</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>బహుమతి</t>
+          <t>ర్యాంక్</t>
         </is>
       </c>
     </row>
@@ -17116,32 +17116,32 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>rank</t>
+          <t>start</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>ક્રમ</t>
+          <t>શરૂ</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>रैंक</t>
+          <t>शुरुआत</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>தரவரிசை</t>
+          <t>தொடக்கம்</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>ర్యాంక్</t>
+          <t>ప్రారంభం</t>
         </is>
       </c>
     </row>
@@ -17153,32 +17153,32 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>start</t>
+          <t>termsAndConditions</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>શરૂ</t>
+          <t>નિયમો અને શરતો</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>शुरुआत</t>
+          <t>नियम और शर्तें</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>தொடக்கம்</t>
+          <t>விதிமுறைகள் மற்றும் நிபந்தனைகள்</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>ప్రారంభం</t>
+          <t>నిబంధనలు మరియు షరతులు</t>
         </is>
       </c>
     </row>
@@ -17190,32 +17190,32 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>termsAndConditions</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Tournament</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>નિયમો અને શરતો</t>
+          <t>ટૂર્નામૅન્ટ</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>नियम और शर्तें</t>
+          <t>टूर्नामेंट</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>விதிமுறைகள் மற்றும் நிபந்தனைகள்</t>
+          <t>போட்டி</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>నిబంధనలు మరియు షరతులు</t>
+          <t>టోర్నమెంట్</t>
         </is>
       </c>
     </row>
@@ -17227,69 +17227,69 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>trophyAlt</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Tournament</t>
+          <t>trophy</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>ટૂર્નામૅન્ટ</t>
+          <t>ટ્રૉફી</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>टूर्नामेंट</t>
+          <t>ट्रॉफी</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>போட்டி</t>
+          <t>கோப்பை</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>టోర్నమెంట్</t>
+          <t>ట్రోఫీ</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>leaderboard</t>
+          <t>locale</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>trophyAlt</t>
+          <t>unavailable.message</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>trophy</t>
+          <t>Language {{locale}} is not available yet. Showing default language.</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>ટ્રૉફી</t>
+          <t>{{locale}} ભાષા હાલમાં ઉપલબ્ધ નથી. મૂળભૂત ભાષા દર્શાવવામાં આવી રહી છે.</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>ट्रॉफी</t>
+          <t>{{locale}} भाषा अभी उपलब्ध नहीं है। डिफ़ॉल्ट भाषा दिखाई जा रही है।</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>கோப்பை</t>
+          <t>{{locale}} மொழி தற்போது கிடைக்கவில்லை. இயல்புநிலை மொழி காட்டப்படுகிறது.</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>ట్రోఫీ</t>
+          <t>{{locale}} భాష ప్రస్తుతం అందుబాటులో లేదు. డిఫాల్ట్ భాషను చూపిస్తున్నాము.</t>
         </is>
       </c>
     </row>
@@ -17301,106 +17301,106 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>unavailable.message</t>
+          <t>unavailable.title</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Language {{locale}} is not available yet. Showing default language.</t>
+          <t>Language unavailable</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>{{locale}} ભાષા હાલમાં ઉપલબ્ધ નથી. મૂળભૂત ભાષા દર્શાવવામાં આવી રહી છે.</t>
+          <t>ભાષા ઉપલબ્ધ નથી</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>{{locale}} भाषा अभी उपलब्ध नहीं है। डिफ़ॉल्ट भाषा दिखाई जा रही है।</t>
+          <t>भाषा उपलब्ध नहीं है</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>{{locale}} மொழி தற்போது கிடைக்கவில்லை. இயல்புநிலை மொழி காட்டப்படுகிறது.</t>
+          <t>மொழி கிடைக்கவில்லை</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>{{locale}} భాష ప్రస్తుతం అందుబాటులో లేదు. డిఫాల్ట్ భాషను చూపిస్తున్నాము.</t>
+          <t>భాష అందుబాటులో లేదు</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>locale</t>
+          <t>notAuthorized</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>unavailable.title</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Language unavailable</t>
+          <t>You are not authorized to access this page.</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>ભાષા ઉપલબ્ધ નથી</t>
+          <t>આ પૃષ્ઠ ઍક્સેસ કરવા માટે તમે અધિકૃત નથી.</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>भाषा उपलब्ध नहीं है</t>
+          <t>आपको इस पेज तक पहुंचने की अनुमति नहीं है।</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>மொழி கிடைக்கவில்லை</t>
+          <t>இந்த பக்கத்தை அணுக உங்களுக்கு அனுமதி இல்லை.</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>భాష అందుబాటులో లేదు</t>
+          <t>ఈ పేజీని యాక్సెస్ చేయడానికి మీకు అనుమతి లేదు.</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>notAuthorized</t>
+          <t>notFound</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>code</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>You are not authorized to access this page.</t>
+          <t>404</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>આ પૃષ્ઠ ઍક્સેસ કરવા માટે તમે અધિકૃત નથી.</t>
+          <t>404</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>आपको इस पेज तक पहुंचने की अनुमति नहीं है।</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>இந்த பக்கத்தை அணுக உங்களுக்கு அனுமதி இல்லை.</t>
+          <t>404</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>ఈ పేజీని యాక్సెస్ చేయడానికి మీకు అనుమతి లేదు.</t>
+          <t>404</t>
         </is>
       </c>
     </row>
@@ -17412,32 +17412,32 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>The page you're looking for doesn't exist or has been moved. Let's get you back to where you belong.</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>જે પૃષ્ઠ તમે શોધી રહ્યા છો તે અસ્તિત્વ ધરાવ્યું નથી અથવા ખસેડવામાં આવ્યું છે. ચાલો તમને પાછા જ્યાં હોવ ત્યાં મોકલીએ.</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>जो पेज आप ढूंढ रहे हैं वह मौजूद नहीं है या हटा दिया गया है। चलिए आपको वापस ले चलते हैं।</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>நீங்கள் தேடும் பக்கம் இல்லை அல்லது நகர்த்தப்பட்டது. திரும்பி செல்வோம்.</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>మీరు వెతుకుతున్న పేజీ లేదు లేదా తరలించబడింది. తిరిగి వెళ్ళండి.</t>
         </is>
       </c>
     </row>
@@ -17449,106 +17449,106 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>title</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>The page you're looking for doesn't exist or has been moved. Let's get you back to where you belong.</t>
+          <t>Oops! Page Not Found</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>જે પૃષ્ઠ તમે શોધી રહ્યા છો તે અસ્તિત્વ ધરાવ્યું નથી અથવા ખસેડવામાં આવ્યું છે. ચાલો તમને પાછા જ્યાં હોવ ત્યાં મોકલીએ.</t>
+          <t>અરે! પૃષ્ઠ મળ્યું નહીં</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>जो पेज आप ढूंढ रहे हैं वह मौजूद नहीं है या हटा दिया गया है। चलिए आपको वापस ले चलते हैं।</t>
+          <t>उफ़! पेज नहीं मिला</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>நீங்கள் தேடும் பக்கம் இல்லை அல்லது நகர்த்தப்பட்டது. திரும்பி செல்வோம்.</t>
+          <t>அச்சச்சோ! பக்கம் கிடைக்கவில்லை</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>మీరు వెతుకుతున్న పేజీ లేదు లేదా తరలించబడింది. తిరిగి వెళ్ళండి.</t>
+          <t>అయ్యో! పేజీ కనుగొనబడలేదు</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>notFound</t>
+          <t>partners</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Oops! Page Not Found</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>અરે! પૃષ્ઠ મળ્યું નહીં</t>
+          <t>પ્રૉવાઇડર</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>उफ़! पेज नहीं मिला</t>
+          <t>प्रदाता</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>அச்சச்சோ! பக்கம் கிடைக்கவில்லை</t>
+          <t>வழங்குநர்</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>అయ్యో! పేజీ కనుగొనబడలేదు</t>
+          <t>ప్రొవైడర్</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>partners</t>
+          <t>profile</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>fields.address</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>પ્રૉવાઇડર</t>
+          <t>સરનામું</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>प्रदाता</t>
+          <t>पता</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>வழங்குநர்</t>
+          <t>முகவரி</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>ప్రొవైడర్</t>
+          <t>చిరునామా</t>
         </is>
       </c>
     </row>
@@ -17560,32 +17560,32 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>fields.address</t>
+          <t>fields.city</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>City</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>સરનામું</t>
+          <t>શહેર</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>पता</t>
+          <t>शहर</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>முகவரி</t>
+          <t>நகரம்</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>చిరునామా</t>
+          <t>నగరం</t>
         </is>
       </c>
     </row>
@@ -17597,32 +17597,32 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>fields.city</t>
+          <t>fields.country</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>શહેર</t>
+          <t>દેશ</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>शहर</t>
+          <t>देश</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>நகரம்</t>
+          <t>நாடு</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>నగరం</t>
+          <t>దేశం</t>
         </is>
       </c>
     </row>
@@ -17634,32 +17634,32 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>fields.country</t>
+          <t>fields.countryCode</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Country Code</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>દેશ</t>
+          <t>દેશ કોડ</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>देश</t>
+          <t>देश कोड</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>நாடு</t>
+          <t>நாட்டு குறியீடு</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>దేశం</t>
+          <t>దేశ కోడ్</t>
         </is>
       </c>
     </row>
@@ -17671,32 +17671,32 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>fields.countryCode</t>
+          <t>fields.currency</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Country Code</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>દેશ કોડ</t>
+          <t>ચલણ</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>देश कोड</t>
+          <t>मुद्रा</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>நாட்டு குறியீடு</t>
+          <t>நாணயம்</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>దేశ కోడ్</t>
+          <t>కరెన్సీ</t>
         </is>
       </c>
     </row>
@@ -17708,32 +17708,32 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>fields.currency</t>
+          <t>fields.dateOfBirth</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>ચલણ</t>
+          <t>જન્મ તારીખ</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>मुद्रा</t>
+          <t>जन्म तिथि</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>நாணயம்</t>
+          <t>பிறந்த தேதி</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>కరెన్సీ</t>
+          <t>పుట్టిన తేదీ</t>
         </is>
       </c>
     </row>
@@ -17745,32 +17745,32 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>fields.dateOfBirth</t>
+          <t>fields.email</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>જન્મ તારીખ</t>
+          <t>ઇ-મેઇલ</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>जन्म तिथि</t>
+          <t>ईमेल</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>பிறந்த தேதி</t>
+          <t>மின்னஞ்சல்</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>పుట్టిన తేదీ</t>
+          <t>ఇమెయిల్</t>
         </is>
       </c>
     </row>
@@ -17782,32 +17782,32 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>fields.email</t>
+          <t>fields.firstName</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>ઇ-મેઇલ</t>
+          <t>પ્રથમ નામ</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>ईमेल</t>
+          <t>पहला नाम</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>மின்னஞ்சல்</t>
+          <t>முதல் பெயர்</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>ఇమెయిల్</t>
+          <t>మొదటి పేరు</t>
         </is>
       </c>
     </row>
@@ -17819,32 +17819,32 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>fields.firstName</t>
+          <t>fields.lastName</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>પ્રથમ નામ</t>
+          <t>છેલ્લું નામ</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>पहला नाम</t>
+          <t>अंतिम नाम</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>முதல் பெயர்</t>
+          <t>கடைசி பெயர்</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>మొదటి పేరు</t>
+          <t>చివరి పేరు</t>
         </is>
       </c>
     </row>
@@ -17856,32 +17856,32 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>fields.lastName</t>
+          <t>fields.phone</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>છેલ્લું નામ</t>
+          <t>ફોન નંબર</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>अंतिम नाम</t>
+          <t>फ़ोन नंबर</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>கடைசி பெயர்</t>
+          <t>தொலைபேசி எண்</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>చివరి పేరు</t>
+          <t>ఫోన్ నంబర్</t>
         </is>
       </c>
     </row>
@@ -17893,32 +17893,32 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>fields.phone</t>
+          <t>fields.state</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>State</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>ફોન નંબર</t>
+          <t>રાજ્ય</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>फ़ोन नंबर</t>
+          <t>राज्य</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>தொலைபேசி எண்</t>
+          <t>மாநிலம்</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>ఫోన్ నంబర్</t>
+          <t>రాష్ట్రం</t>
         </is>
       </c>
     </row>
@@ -17930,32 +17930,32 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>fields.state</t>
+          <t>fields.userName</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Username</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>રાજ્ય</t>
+          <t>વપરાશકર્તા નામ</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>राज्य</t>
+          <t>उपयोगकर्ता नाम</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>மாநிலம்</t>
+          <t>பயனர்பெயர்</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>రాష్ట్రం</t>
+          <t>వినియోగదారు పేరు</t>
         </is>
       </c>
     </row>
@@ -17967,32 +17967,32 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>fields.userName</t>
+          <t>fields.zipCode</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Username</t>
+          <t>Zip Code</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>વપરાશકર્તા નામ</t>
+          <t>ઝિપ કોડ</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>उपयोगकर्ता नाम</t>
+          <t>पिन कोड</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>பயனர்பெயர்</t>
+          <t>அஞ்சல் குறியீடு</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>వినియోగదారు పేరు</t>
+          <t>జిప్ కోడ్</t>
         </is>
       </c>
     </row>
@@ -18004,32 +18004,32 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>fields.zipCode</t>
+          <t>personalDetails</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Zip Code</t>
+          <t>Your Personal Details</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>ઝિપ કોડ</t>
+          <t>તમારી વ્યક્તિગત વિગતો</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>पिन कोड</t>
+          <t>आपकी व्यक्तिगत जानकारी</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>அஞ்சல் குறியீடு</t>
+          <t>உங்கள் தனிப்பட்ட விவரங்கள்</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>జిప్ కోడ్</t>
+          <t>మీ వ్యక్తిగత వివరాలు</t>
         </is>
       </c>
     </row>
@@ -18041,32 +18041,32 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>personalDetails</t>
+          <t>playerId</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Your Personal Details</t>
+          <t>Player ID: {{id}}</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>તમારી વ્યક્તિગત વિગતો</t>
+          <t>પ્લેયર આઈડી: {{id}}</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>आपकी व्यक्तिगत जानकारी</t>
+          <t>प्लेयर आईडी: {{id}}</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>உங்கள் தனிப்பட்ட விவரங்கள்</t>
+          <t>பிளேயர் ஐடி: {{id}}</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>మీ వ్యక్తిగత వివరాలు</t>
+          <t>ప్లేయర్ ఐడి: {{id}}</t>
         </is>
       </c>
     </row>
@@ -20927,32 +20927,32 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>enterAmountPlaceholder</t>
+          <t>addAccount</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Enter Amount</t>
+          <t>Add account</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>રકમ દાખલ કરો</t>
+          <t>ખાતું ઉમેરો</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>राशि दर्ज करें</t>
+          <t>खाता जोड़ें</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>தொகையை உள்ளிடவும்</t>
+          <t>கணக்கைச் சேர்</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>మొత్తాన్ని నమోదు చేయండి</t>
+          <t>ఖాతాను జోడించు</t>
         </is>
       </c>
     </row>
@@ -20964,32 +20964,32 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>selectBankPlaceholder</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Select Bank Account</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>બધું</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>बैंक खाता चुनें</t>
+          <t>सभी</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>வங்கி கணக்கை தேர்வு செய்யவும்</t>
+          <t>அனைத்தும்</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>బ్యాంకు ఖాతాను ఎంచుకోండి</t>
+          <t>అన్నీ</t>
         </is>
       </c>
     </row>
@@ -21001,32 +21001,32 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>amountLabel</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Withdraw</t>
+          <t>Amount (₹)</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>ઉપાડ કરો</t>
+          <t>રકમ (₹)</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>निकालें</t>
+          <t>राशि (₹)</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>திரும்பப் பெறுக</t>
+          <t>தொகை (₹)</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>ఉపసంహరించుకో</t>
+          <t>మొత్తం (₹)</t>
         </is>
       </c>
     </row>
@@ -21038,32 +21038,32 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>submitting</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Withdrawing…</t>
+          <t>Available for withdrawal</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>ઉપાડ થઈ રહ્યો છે…</t>
+          <t>ઉપાડ માટે ઉપલબ્ધ</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>निकाला जा रहा है…</t>
+          <t>निकासी के लिए उपलब्ध</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>திரும்பப் பெறுகிறது…</t>
+          <t>திரும்பப் பெறக் கிடைக்கும்</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>ఉపసంహరిస్తోంది…</t>
+          <t>ఉపసంహరణకు అందుబాటులో ఉంది</t>
         </is>
       </c>
     </row>
@@ -21075,32 +21075,32 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>bankAccount</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Withdraw</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>ઉપાડ</t>
+          <t>બૅન્ક ખાતું</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>निकासी</t>
+          <t>बैंक खाता</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>திரும்பப் பெறுதல்</t>
+          <t>வங்கி கணக்கு</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>ఉపసంహరణ</t>
+          <t>బ్యాంకు ఖాతా</t>
         </is>
       </c>
     </row>
@@ -21112,32 +21112,32 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>toasts.error</t>
+          <t>enterAmountPlaceholder</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Failed to process withdrawal.</t>
+          <t>Enter Amount</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>ઉપાડ પ્રક્રિયા કરવામાં નિષ્ફળ.</t>
+          <t>રકમ દાખલ કરો</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>निकासी प्रसंस्कृत करने में विफल।</t>
+          <t>राशि दर्ज करें</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>திரும்பப் பெறுதலை செயலாக்க தோல்வி.</t>
+          <t>தொகையை உள்ளிடவும்</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>ఉపసంహరణ ప్రాసెస్ చేయడం విఫలమైంది.</t>
+          <t>మొత్తాన్ని నమోదు చేయండి</t>
         </is>
       </c>
     </row>
@@ -21149,32 +21149,32 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>toasts.success</t>
+          <t>info.dailyTransactionLimit</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Amount Withdrawal successfully.</t>
+          <t>Max Per Day Transaction Limit</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>રકમ સફળતાપૂર્વક ઉપાડવામાં આવી.</t>
+          <t>દિવસ દીઠ મહત્તમ વ્યવહાર મર્યાદા</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>राशि सफलतापूर्वक निकाली गई।</t>
+          <t>प्रति दिन अधिकतम लेनदेन सीमा</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>தொகை வெற்றிகரமாக திரும்பப் பெறப்பட்டது.</t>
+          <t>ஒரு நாளுக்கான அதிகபட்ச பரிவர்த்தனை வரம்பு</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>మొత్తం విజయవంతంగా ఉపసంహరించబడింది.</t>
+          <t>రోజుకు గరిష్ఠ లావాదేవీ పరిమితి</t>
         </is>
       </c>
     </row>
@@ -21186,32 +21186,32 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>validation.amountExceedsMax</t>
+          <t>info.maxPerDay</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>You can withdraw a maximum of ₹{{max}}</t>
+          <t>Max Per Day</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>તમે મહત્તમ ₹{{max}} ઉપાડ કરી શકો છો</t>
+          <t>દિવસ દીઠ મહત્તમ</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>आप अधिकतम ₹{{max}} निकाल सकते हैं</t>
+          <t>प्रति दिन अधिकतम</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>அதிகபட்சம் ₹{{max}} திரும்பப் பெறலாம்</t>
+          <t>ஒரு நாளுக்கு அதிகபட்சம்</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>మీరు గరిష్టంగా ₹{{max}} ఉపసంహరించుకోవచ్చు</t>
+          <t>రోజుకు గరిష్ఠం</t>
         </is>
       </c>
     </row>
@@ -21223,32 +21223,32 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>validation.amountMinimum</t>
+          <t>info.min</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Amount must be greater than ₹500</t>
+          <t>Min Withdrawal</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>રકમ ₹500 કરતાં વધારે હોવી જોઈએ</t>
+          <t>ન્યૂનતમ ઉપાડ</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>राशि ₹500 से अधिक होनी चाहिए</t>
+          <t>न्यूनतम निकासी</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>தொகை ₹500 ஐ விட அதிகமாக இருக்க வேண்டும்</t>
+          <t>குறைந்தபட்ச திரும்பப் பெறுதல்</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>మొత్తం ₹500 కంటే ఎక్కువగా ఉండాలి</t>
+          <t>కనీస ఉపసంహరణ</t>
         </is>
       </c>
     </row>
@@ -21260,32 +21260,32 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>validation.amountNumbersOnly</t>
+          <t>info.title</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Amount must contain only numbers</t>
+          <t>Withdrawal Info</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>રકમ ફક્ત સંખ્યા ધરાવવી જોઈએ</t>
+          <t>ઉપાડ માહિતી</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>राशि में केवल संख्याएं होनी चाहिए</t>
+          <t>निकासी जानकारी</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>தொகையில் எண்கள் மட்டுமே இருக்க வேண்டும்</t>
+          <t>திரும்பப் பெறுதல் தகவல்</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>మొత్తంలో సంఖ్యలు మాత్రమే ఉండాలి</t>
+          <t>ఉపసంహరణ సమాచారం</t>
         </is>
       </c>
     </row>
@@ -21297,32 +21297,32 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>validation.amountRequired</t>
+          <t>noBank</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Amount is required</t>
+          <t>No bank account added</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>રકમ જરૂરી છે</t>
+          <t>કોઈ બૅન્ક ખાતું ઉમેરાયું નથી</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>राशि आवश्यक है</t>
+          <t>कोई बैंक खाता नहीं जोड़ा गया</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>தொகை தேவை</t>
+          <t>வங்கி கணக்கு எதுவும் சேர்க்கப்படவில்லை</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>మొత్తం అవసరం</t>
+          <t>బ్యాంకు ఖాతా ఏదీ జోడించలేదు</t>
         </is>
       </c>
     </row>
@@ -21334,32 +21334,32 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>validation.bankRequired</t>
+          <t>noBankHint</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Select Bank Account</t>
+          <t>Add one to withdraw your balance</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>બૅન્ક ખાતું પસંદ કરો</t>
+          <t>તમારું બૅલૅન્સ ઉપાડવા માટે એક ખાતું ઉમેરો</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>बैंक खाता चुनें</t>
+          <t>अपना बैलेंस निकालने के लिए एक खाता जोड़ें</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>வங்கி கணக்கை தேர்வு செய்யவும்</t>
+          <t>உங்கள் இருப்பைத் திரும்பப் பெற ஒரு கணக்கைச் சேர்க்கவும்</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>బ్యాంకు ఖాతాను ఎంచుకోండి</t>
+          <t>మీ బ్యాలెన్స్‌ను ఉపసంహరించడానికి ఒక ఖాతాను జోడించండి</t>
         </is>
       </c>
     </row>
@@ -21371,32 +21371,32 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>whatsappCta</t>
+          <t>selectBankPlaceholder</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Withdrawal via WhatsApp</t>
+          <t>Select Bank Account</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>WhatsApp દ્વારા ઉપાડ</t>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>व्हाट्सऐप के जरिए निकासी</t>
+          <t>बैंक खाता चुनें</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>வாட்ஸ்அப் மூலம் திரும்பப் பெறுதல்</t>
+          <t>வங்கி கணக்கை தேர்வு செய்யவும்</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>వాట్సాప్ ద్వారా ఉపసంహరణ</t>
+          <t>బ్యాంకు ఖాతాను ఎంచుకోండి</t>
         </is>
       </c>
     </row>
@@ -21408,30 +21408,474 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
+          <t>submit</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Withdraw</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>ઉપાડ કરો</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>निकालें</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>திரும்பப் பெறுக</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>ఉపసంహరించుకో</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>submitting</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Withdrawing…</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>ઉપાડ થઈ રહ્યો છે…</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>निकाला जा रहा है…</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>திரும்பப் பெறுகிறது…</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>ఉపసంహరిస్తోంది…</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Withdraw</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>ઉપાડ</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>निकासी</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>திரும்பப் பெறுதல்</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>ఉపసంహరణ</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>toasts.error</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Failed to process withdrawal.</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>ઉપાડ પ્રક્રિયા કરવામાં નિષ્ફળ.</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>निकासी प्रसंस्कृत करने में विफल।</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>திரும்பப் பெறுதலை செயலாக்க தோல்வி.</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>ఉపసంహరణ ప్రాసెస్ చేయడం విఫలమైంది.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>toasts.success</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Amount Withdrawal successfully.</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>રકમ સફળતાપૂર્વક ઉપાડવામાં આવી.</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>राशि सफलतापूर्वक निकाली गई।</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>தொகை வெற்றிகரமாக திரும்பப் பெறப்பட்டது.</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>మొత్తం విజయవంతంగా ఉపసంహరించబడింది.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>validation.amountExceedsMax</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>You can withdraw a maximum of ₹{{max}}</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>તમે મહત્તમ ₹{{max}} ઉપાડ કરી શકો છો</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>आप अधिकतम ₹{{max}} निकाल सकते हैं</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>அதிகபட்சம் ₹{{max}} திரும்பப் பெறலாம்</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>మీరు గరిష్టంగా ₹{{max}} ఉపసంహరించుకోవచ్చు</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>validation.amountMinimum</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Amount must be greater than ₹500</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>રકમ ₹500 કરતાં વધારે હોવી જોઈએ</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>राशि ₹500 से अधिक होनी चाहिए</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>தொகை ₹500 ஐ விட அதிகமாக இருக்க வேண்டும்</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>మొత్తం ₹500 కంటే ఎక్కువగా ఉండాలి</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>validation.amountNumbersOnly</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Amount must contain only numbers</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>રકમ ફક્ત સંખ્યા ધરાવવી જોઈએ</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>राशि में केवल संख्याएं होनी चाहिए</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>தொகையில் எண்கள் மட்டுமே இருக்க வேண்டும்</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>మొత్తంలో సంఖ్యలు మాత్రమే ఉండాలి</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>validation.amountRequired</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Amount is required</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>રકમ જરૂરી છે</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>राशि आवश्यक है</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>தொகை தேவை</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>మొత్తం అవసరం</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>validation.bankRequired</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Select Bank Account</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>બૅન્ક ખાતું પસંદ કરો</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>बैंक खाता चुनें</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>வங்கி கணக்கை தேர்வு செய்யவும்</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>బ్యాంకు ఖాతాను ఎంచుకోండి</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>whatsappCta</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Withdrawal via WhatsApp</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>WhatsApp દ્વારા ઉપાડ</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>व्हाट्सऐप के जरिए निकासी</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>வாட்ஸ்அப் மூலம் திரும்பப் பெறுதல்</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>వాట్సాప్ ద్వారా ఉపసంహరణ</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>withdrawNow</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Withdraw Now</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>હમણાં ઉપાડ કરો</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>अभी निकालें</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>இப்போது திரும்பப் பெறுக</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>ఇప్పుడే ఉపసంహరించుకో</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>withdraw</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
           <t>withdrawableMoney</t>
         </is>
       </c>
-      <c r="C568" t="inlineStr">
+      <c r="C580" t="inlineStr">
         <is>
           <t>Withdrawal Balance</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr">
+      <c r="D580" t="inlineStr">
         <is>
           <t>ઉપાડ બૅલૅન્સ</t>
         </is>
       </c>
-      <c r="E568" t="inlineStr">
+      <c r="E580" t="inlineStr">
         <is>
           <t>निकासी बैलेंस</t>
         </is>
       </c>
-      <c r="F568" t="inlineStr">
+      <c r="F580" t="inlineStr">
         <is>
           <t>திரும்பப் பெறக்கூடிய இருப்பு</t>
         </is>
       </c>
-      <c r="G568" t="inlineStr">
+      <c r="G580" t="inlineStr">
         <is>
           <t>ఉపసంహరణ బ్యాలెన్స్</t>
         </is>
